--- a/academy/web/public/research/stoic-qca/stoic_qca_codebook.xlsx
+++ b/academy/web/public/research/stoic-qca/stoic_qca_codebook.xlsx
@@ -21672,7 +21672,7 @@
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Score may be too low: the codebook puts slavery at ADV 1, and Arnold says 'good authorities' (Gellius 2.18.8, Athenaeus, both not in corpus) make Persaeus Zeno's servant (oiketes) before he became his fellow-lodger. Arnold also cites Seneca for Zeno having no slave, and Seneca, Consolation to Helvia 12.4, says Zeno 'had none' (in the corpus as chunk fd773923-fb41-43aa-b146-5c393e39f200, which is mislabelled there as Consolation to Polybius), so the slavery is contested. Suggest 1 if the Gellius tradition is accepted, otherwise keep 0.67 and note the dispute. The DL 7.36 estate loss was a false report, so it is not adversity.</t>
+          <t xml:space="preserve">Score may be too low: the codebook puts slavery at ADV 1, and Arnold says 'good authorities' (Gellius 2.18.8, Athenaeus, both not in corpus) make Persaeus Zeno's servant (oiketes) before he became his fellow-lodger. Arnold also cites Seneca for Zeno having no slave, and Seneca, Consolation to Helvia 12.4, says Zeno 'had none' (in the corpus as chunk fd773923-fb41-43aa-b146-5c393e39f200), so the slavery is contested. Suggest 1 if the Gellius tradition is accepted, otherwise keep 0.67 and note the dispute. The DL 7.36 estate loss was a false report, so it is not adversity.</t>
         </is>
       </c>
       <c r="I168" s="6" t="inlineStr">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Score may be too low: the codebook puts slavery at ADV 1, and Arnold says 'good authorities' (Gellius 2.18.8, Athenaeus, both not in corpus) make Persaeus Zeno's servant (oiketes) before he became his fellow-lodger. Arnold also cites Seneca for Zeno having no slave, and Seneca, Consolation to Helvia 12.4, says Zeno 'had none' (in the corpus as chunk fd773923-fb41-43aa-b146-5c393e39f200, which is mislabelled there as Consolation to Polybius), so the slavery is contested. Suggest 1 if the Gellius tradition is accepted, otherwise keep 0.67 and note the dispute. The DL 7.36 estate loss was a false report, so it is not adversity.</t>
+          <t xml:space="preserve">Score may be too low: the codebook puts slavery at ADV 1, and Arnold says 'good authorities' (Gellius 2.18.8, Athenaeus, both not in corpus) make Persaeus Zeno's servant (oiketes) before he became his fellow-lodger. Arnold also cites Seneca for Zeno having no slave, and Seneca, Consolation to Helvia 12.4, says Zeno 'had none' (in the corpus as chunk fd773923-fb41-43aa-b146-5c393e39f200), so the slavery is contested. Suggest 1 if the Gellius tradition is accepted, otherwise keep 0.67 and note the dispute. The DL 7.36 estate loss was a false report, so it is not adversity.</t>
         </is>
       </c>
       <c r="I169" s="6" t="inlineStr">
@@ -21794,7 +21794,7 @@
       </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Score may be too low: the codebook puts slavery at ADV 1, and Arnold says 'good authorities' (Gellius 2.18.8, Athenaeus, both not in corpus) make Persaeus Zeno's servant (oiketes) before he became his fellow-lodger. Arnold also cites Seneca for Zeno having no slave, and Seneca, Consolation to Helvia 12.4, says Zeno 'had none' (in the corpus as chunk fd773923-fb41-43aa-b146-5c393e39f200, which is mislabelled there as Consolation to Polybius), so the slavery is contested. Suggest 1 if the Gellius tradition is accepted, otherwise keep 0.67 and note the dispute. The DL 7.36 estate loss was a false report, so it is not adversity.</t>
+          <t xml:space="preserve">Score may be too low: the codebook puts slavery at ADV 1, and Arnold says 'good authorities' (Gellius 2.18.8, Athenaeus, both not in corpus) make Persaeus Zeno's servant (oiketes) before he became his fellow-lodger. Arnold also cites Seneca for Zeno having no slave, and Seneca, Consolation to Helvia 12.4, says Zeno 'had none' (in the corpus as chunk fd773923-fb41-43aa-b146-5c393e39f200), so the slavery is contested. Suggest 1 if the Gellius tradition is accepted, otherwise keep 0.67 and note the dispute. The DL 7.36 estate loss was a false report, so it is not adversity.</t>
         </is>
       </c>
       <c r="I170" s="6" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Score may be too low: the codebook puts slavery at ADV 1, and Arnold says 'good authorities' (Gellius 2.18.8, Athenaeus, both not in corpus) make Persaeus Zeno's servant (oiketes) before he became his fellow-lodger. Arnold also cites Seneca for Zeno having no slave, and Seneca, Consolation to Helvia 12.4, says Zeno 'had none' (in the corpus as chunk fd773923-fb41-43aa-b146-5c393e39f200, which is mislabelled there as Consolation to Polybius), so the slavery is contested. Suggest 1 if the Gellius tradition is accepted, otherwise keep 0.67 and note the dispute. The DL 7.36 estate loss was a false report, so it is not adversity.</t>
+          <t xml:space="preserve">Score may be too low: the codebook puts slavery at ADV 1, and Arnold says 'good authorities' (Gellius 2.18.8, Athenaeus, both not in corpus) make Persaeus Zeno's servant (oiketes) before he became his fellow-lodger. Arnold also cites Seneca for Zeno having no slave, and Seneca, Consolation to Helvia 12.4, says Zeno 'had none' (in the corpus as chunk fd773923-fb41-43aa-b146-5c393e39f200), so the slavery is contested. Suggest 1 if the Gellius tradition is accepted, otherwise keep 0.67 and note the dispute. The DL 7.36 estate loss was a false report, so it is not adversity.</t>
         </is>
       </c>
       <c r="I171" s="6" t="inlineStr">
@@ -24601,7 +24601,7 @@
       <c r="H220" s="6"/>
       <c r="I220" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seneca, Consolation to Helvia 18 (corpus chunk labelled 'Consolation to Polybius')</t>
+          <t xml:space="preserve">Seneca, Consolation to Helvia 18</t>
         </is>
       </c>
       <c r="J220" s="6" t="inlineStr">
@@ -24614,11 +24614,7 @@
           <t xml:space="preserve">6e147062-fcd3-4293-9898-6bea4c0cdde9</t>
         </is>
       </c>
-      <c r="L220" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corpus work labels for the two consolations appear swapped: this text is To Helvia.</t>
-        </is>
-      </c>
+      <c r="L220" s="6"/>
       <c r="M220" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://academy.pursuearete.com/library?chunk=6e147062-fcd3-4293-9898-6bea4c0cdde9&amp;q=I+shall+make+no+complaints+about+my+childlessness</t>
@@ -25240,7 +25236,7 @@
       <c r="H231" s="6"/>
       <c r="I231" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seneca, On Clemency 1.1 (corpus chunk labelled 'Consolation to Helvia')</t>
+          <t xml:space="preserve">Seneca, On Clemency 1.1</t>
         </is>
       </c>
       <c r="J231" s="6" t="inlineStr">
@@ -25253,11 +25249,7 @@
           <t xml:space="preserve">a390ff9a-e243-4e32-bbcf-858ea2f4ae65</t>
         </is>
       </c>
-      <c r="L231" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The opening of On Clemency sits in a chunk labelled Consolation to Helvia.</t>
-        </is>
-      </c>
+      <c r="L231" s="6"/>
       <c r="M231" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://academy.pursuearete.com/library?chunk=a390ff9a-e243-4e32-bbcf-858ea2f4ae65&amp;q=I+have+determined+to+write+a+book+upon</t>
@@ -25301,7 +25293,7 @@
       <c r="H232" s="6"/>
       <c r="I232" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seneca, Consolation to Polybius 13 (corpus chunk labelled 'Consolation to Helvia')</t>
+          <t xml:space="preserve">Seneca, Consolation to Polybius 13</t>
         </is>
       </c>
       <c r="J232" s="6" t="inlineStr">
@@ -25316,7 +25308,7 @@
       </c>
       <c r="L232" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shows dependence on the emperor's favour; text is To Polybius despite the label.</t>
+          <t xml:space="preserve">Shows dependence on the emperor's favour.</t>
         </is>
       </c>
       <c r="M232" s="6" t="inlineStr">

--- a/academy/web/public/research/stoic-qca/stoic_qca_codebook.xlsx
+++ b/academy/web/public/research/stoic-qca/stoic_qca_codebook.xlsx
@@ -24271,7 +24271,7 @@
       </c>
       <c r="I214" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (preface to Seneca's Morals, after Lipsius, paraphrasing Tacitus; secondary, early modern; corpus labels it author Seneca, work Morals)</t>
+          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (1678, prefixed to his Seneca's Morals; much of it renders Tacitus; scholarship)</t>
         </is>
       </c>
       <c r="J214" s="6" t="inlineStr">
@@ -24381,7 +24381,7 @@
       <c r="H216" s="6"/>
       <c r="I216" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (preface to Seneca's Morals, after Lipsius, paraphrasing Tacitus; secondary, early modern; corpus labels it author Seneca, work Morals)</t>
+          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (1678, prefixed to his Seneca's Morals; much of it renders Tacitus; scholarship)</t>
         </is>
       </c>
       <c r="J216" s="6" t="inlineStr">
@@ -24715,7 +24715,7 @@
       <c r="H222" s="6"/>
       <c r="I222" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (preface to Seneca's Morals, after Lipsius, paraphrasing Tacitus; secondary, early modern; corpus labels it author Seneca, work Morals)</t>
+          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (1678, prefixed to his Seneca's Morals; much of it renders Tacitus; scholarship)</t>
         </is>
       </c>
       <c r="J222" s="6" t="inlineStr">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="I227" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (preface to Seneca's Morals, after Lipsius, paraphrasing Tacitus; secondary, early modern; corpus labels it author Seneca, work Morals)</t>
+          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (1678, prefixed to his Seneca's Morals; much of it renders Tacitus; scholarship)</t>
         </is>
       </c>
       <c r="J227" s="6" t="inlineStr">
@@ -25122,7 +25122,7 @@
       <c r="H229" s="6"/>
       <c r="I229" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (preface to Seneca's Morals, after Lipsius, paraphrasing Tacitus; secondary, early modern; corpus labels it author Seneca, work Morals)</t>
+          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (1678, prefixed to his Seneca's Morals; much of it renders Tacitus; scholarship)</t>
         </is>
       </c>
       <c r="J229" s="6" t="inlineStr">
@@ -25179,7 +25179,7 @@
       <c r="H230" s="6"/>
       <c r="I230" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (preface to Seneca's Morals, after Lipsius, paraphrasing Tacitus; secondary, early modern; corpus labels it author Seneca, work Morals)</t>
+          <t xml:space="preserve">Roger L'Estrange, 'Seneca's Life and Death' (1678, prefixed to his Seneca's Morals; much of it renders Tacitus; scholarship)</t>
         </is>
       </c>
       <c r="J230" s="6" t="inlineStr">
